--- a/NECP Scenario/Results/Regional Results/KARPATHOS_Generation.xlsx
+++ b/NECP Scenario/Results/Regional Results/KARPATHOS_Generation.xlsx
@@ -563,25 +563,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3.332979601831105E-08</v>
+        <v>4.924213769678411E-08</v>
       </c>
       <c r="C3">
-        <v>1.917507814780849E-08</v>
+        <v>2.832912154565875E-08</v>
       </c>
       <c r="D3">
-        <v>0.01693142611576792</v>
+        <v>0.016931321167063</v>
       </c>
       <c r="E3">
-        <v>0.2987503200219727</v>
+        <v>0.3493459068407793</v>
       </c>
       <c r="F3">
-        <v>0.3507809888517743</v>
+        <v>0.3934014447551455</v>
       </c>
       <c r="G3">
-        <v>0.3780479156001373</v>
+        <v>0.4480881190028188</v>
       </c>
       <c r="H3">
-        <v>0.4419348937341971</v>
+        <v>0.4952803962116404</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -589,25 +589,25 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2.833032661778625E-08</v>
+        <v>4.185581704406655E-08</v>
       </c>
       <c r="C4">
-        <v>1.629881642785907E-08</v>
+        <v>2.407975331561E-08</v>
       </c>
       <c r="D4">
-        <v>0.01439171219840353</v>
+        <v>0.01439162299200046</v>
       </c>
       <c r="E4">
-        <v>0.2539377720170016</v>
+        <v>0.2969440208148936</v>
       </c>
       <c r="F4">
-        <v>0.2981638405240227</v>
+        <v>0.3343912796526486</v>
       </c>
       <c r="G4">
-        <v>0.3213407282600759</v>
+        <v>0.3808749011524921</v>
       </c>
       <c r="H4">
-        <v>0.3756446596741777</v>
+        <v>0.4209883367799129</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -849,25 +849,25 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>0.03857858559353142</v>
+        <v>0.03857858672348548</v>
       </c>
       <c r="C14">
-        <v>0.04387076757241492</v>
+        <v>0.04387076806835825</v>
       </c>
       <c r="D14">
-        <v>0.04839632308290808</v>
+        <v>0.04839631107498488</v>
       </c>
       <c r="E14">
-        <v>0.04416769824878641</v>
+        <v>0.04358315268162104</v>
       </c>
       <c r="F14">
-        <v>0.05329372043862469</v>
+        <v>0.05302142627912736</v>
       </c>
       <c r="G14">
-        <v>0.06594632315389647</v>
+        <v>0.06594636563011948</v>
       </c>
       <c r="H14">
-        <v>0.08729648315320163</v>
+        <v>0.08729672433862126</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1213,25 +1213,25 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>0.1167368026850227</v>
+        <v>0.1167368266087328</v>
       </c>
       <c r="C28">
-        <v>0.1357454352627707</v>
+        <v>0.1357454468662833</v>
       </c>
       <c r="D28">
-        <v>0.02038140623490829</v>
+        <v>0.02038143338436595</v>
       </c>
       <c r="E28">
-        <v>3.952523865673847E-08</v>
+        <v>5.838827943263147E-08</v>
       </c>
       <c r="F28">
-        <v>4.055785866316322E-08</v>
+        <v>6.004070816909494E-08</v>
       </c>
       <c r="G28">
-        <v>0.0004400449940960637</v>
+        <v>0.0004400674735804151</v>
       </c>
       <c r="H28">
-        <v>0.001144245132077285</v>
+        <v>0.0005283806403977601</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1239,25 +1239,25 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>0.03316386438929592</v>
+        <v>0.03316387118110212</v>
       </c>
       <c r="C29">
-        <v>0.03856404410358546</v>
+        <v>0.0385640473975754</v>
       </c>
       <c r="D29">
-        <v>0.005790172218239748</v>
+        <v>0.005790179927535949</v>
       </c>
       <c r="E29">
-        <v>1.121760634023867E-08</v>
+        <v>1.657110783481098E-08</v>
       </c>
       <c r="F29">
-        <v>1.150571804600783E-08</v>
+        <v>1.703280364487038E-08</v>
       </c>
       <c r="G29">
-        <v>0.0001250127583007046</v>
+        <v>0.000125019133031182</v>
       </c>
       <c r="H29">
-        <v>0.0003250694935393889</v>
+        <v>0.0001501079205967252</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1271,19 +1271,19 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>0.02672462506532111</v>
+        <v>0.02672397774092379</v>
       </c>
       <c r="E30">
-        <v>0.09448138176459868</v>
+        <v>0.09525219706762048</v>
       </c>
       <c r="F30">
-        <v>0.1219923319565332</v>
+        <v>0.1379653667902262</v>
       </c>
       <c r="G30">
-        <v>0.2173449911643859</v>
+        <v>0.2116635935393339</v>
       </c>
       <c r="H30">
-        <v>0.2582645746803588</v>
+        <v>0.2551347238380481</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1291,25 +1291,25 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>0.00192701936044231</v>
+        <v>0.001927018181259114</v>
       </c>
       <c r="C31">
-        <v>0.001927020760914061</v>
+        <v>0.001927020247952616</v>
       </c>
       <c r="D31">
-        <v>0.001539473947221857</v>
+        <v>0.001538529505624546</v>
       </c>
       <c r="E31">
-        <v>0.001925669455524841</v>
+        <v>0.001925077735947812</v>
       </c>
       <c r="F31">
-        <v>0.001924921611934576</v>
+        <v>0.001918305312725894</v>
       </c>
       <c r="G31">
-        <v>0.001921192759682482</v>
+        <v>0.001803048415043744</v>
       </c>
       <c r="H31">
-        <v>0.001905499938635928</v>
+        <v>0.001768632837114212</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1323,19 +1323,19 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>5.621453972397355E-08</v>
+        <v>8.308741807325186E-08</v>
       </c>
       <c r="E32">
-        <v>0.01407274876959581</v>
+        <v>0.01469073756880598</v>
       </c>
       <c r="F32">
-        <v>0.01755010300181078</v>
+        <v>0.01783572244091155</v>
       </c>
       <c r="G32">
-        <v>0.01822222703929998</v>
+        <v>0.01822223444678056</v>
       </c>
       <c r="H32">
-        <v>0.01838819912092839</v>
+        <v>0.01838816615948078</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1343,25 +1343,25 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>0.002043305299563311</v>
+        <v>0.002043304186044727</v>
       </c>
       <c r="C33">
-        <v>0.002043306615205451</v>
+        <v>0.002043306127854978</v>
       </c>
       <c r="D33">
-        <v>0.002043275729913231</v>
+        <v>0.002043260877646303</v>
       </c>
       <c r="E33">
-        <v>0.001908636097605214</v>
+        <v>0.001875192884219932</v>
       </c>
       <c r="F33">
-        <v>0.001894602566596571</v>
+        <v>0.001881277314408049</v>
       </c>
       <c r="G33">
-        <v>0.001982051869674752</v>
+        <v>0.001982002026241157</v>
       </c>
       <c r="H33">
-        <v>0.002024141518871702</v>
+        <v>0.002023933538813119</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1427,19 +1427,19 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>0.01548728855207111</v>
+        <v>0.01548779617801921</v>
       </c>
       <c r="E36">
-        <v>0.8041517681365791</v>
+        <v>0.7922198328584893</v>
       </c>
       <c r="F36">
-        <v>0.8007757569679891</v>
+        <v>0.7757229534266359</v>
       </c>
       <c r="G36">
-        <v>0.7648887988385327</v>
+        <v>0.7436994535177877</v>
       </c>
       <c r="H36">
-        <v>0.7668290146673891</v>
+        <v>0.7464348232376163</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1447,25 +1447,25 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>0.004275024951090381</v>
+        <v>0.004275022894787435</v>
       </c>
       <c r="C37">
-        <v>0.004275027389389383</v>
+        <v>0.004275026496142548</v>
       </c>
       <c r="D37">
-        <v>0.002382157306968087</v>
+        <v>0.002383205755144731</v>
       </c>
       <c r="E37">
-        <v>0.003351561666953638</v>
+        <v>0.003327469997907865</v>
       </c>
       <c r="F37">
-        <v>0.003250636348633731</v>
+        <v>0.003235832356563499</v>
       </c>
       <c r="G37">
-        <v>0.003208814049691162</v>
+        <v>0.003083462004765047</v>
       </c>
       <c r="H37">
-        <v>0.003165260185983319</v>
+        <v>0.003025990490168542</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1473,25 +1473,25 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>9.120311085347696E-09</v>
+        <v>1.34693158196958E-08</v>
       </c>
       <c r="C38">
-        <v>3.965898219100311E-09</v>
+        <v>5.859456953005331E-09</v>
       </c>
       <c r="D38">
-        <v>0.01691241902365591</v>
+        <v>0.0169124156079455</v>
       </c>
       <c r="E38">
-        <v>0.1125511869399761</v>
+        <v>0.1228016482379749</v>
       </c>
       <c r="F38">
-        <v>0.1279018589366555</v>
+        <v>0.1504807067672484</v>
       </c>
       <c r="G38">
-        <v>0.1660404949150903</v>
+        <v>0.1903549120693648</v>
       </c>
       <c r="H38">
-        <v>0.1918341322157995</v>
+        <v>0.2163979469409375</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1525,25 +1525,25 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>3.332979601831105E-08</v>
+        <v>4.924213769678411E-08</v>
       </c>
       <c r="C40">
-        <v>1.917507814780849E-08</v>
+        <v>2.832912154565875E-08</v>
       </c>
       <c r="D40">
-        <v>0.01693142611576792</v>
+        <v>0.016931321167063</v>
       </c>
       <c r="E40">
-        <v>0.2987503200219727</v>
+        <v>0.3493459068407793</v>
       </c>
       <c r="F40">
-        <v>0.3507809888517743</v>
+        <v>0.3934014447551455</v>
       </c>
       <c r="G40">
-        <v>0.3780479156001373</v>
+        <v>0.4480881190028188</v>
       </c>
       <c r="H40">
-        <v>0.4419348937341971</v>
+        <v>0.4952803962116404</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1551,25 +1551,25 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>2.833032661778625E-08</v>
+        <v>4.185581704406655E-08</v>
       </c>
       <c r="C41">
-        <v>1.629881642785907E-08</v>
+        <v>2.407975331561E-08</v>
       </c>
       <c r="D41">
-        <v>0.01439171219840353</v>
+        <v>0.01439162299200046</v>
       </c>
       <c r="E41">
-        <v>0.2539377720170016</v>
+        <v>0.2969440208148936</v>
       </c>
       <c r="F41">
-        <v>0.2981638405240227</v>
+        <v>0.3343912796526486</v>
       </c>
       <c r="G41">
-        <v>0.3213407282600759</v>
+        <v>0.3808749011524921</v>
       </c>
       <c r="H41">
-        <v>0.3756446596741777</v>
+        <v>0.4209883367799129</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1577,25 +1577,25 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>-4.999469400524801E-09</v>
+        <v>-7.386320652717561E-09</v>
       </c>
       <c r="C42">
-        <v>-2.87626171994942E-09</v>
+        <v>-4.249368230048754E-09</v>
       </c>
       <c r="D42">
-        <v>-0.002539713917364381</v>
+        <v>-0.002539698175062537</v>
       </c>
       <c r="E42">
-        <v>-0.04481254800497103</v>
+        <v>-0.05240188602588569</v>
       </c>
       <c r="F42">
-        <v>-0.05261714832775166</v>
+        <v>-0.0590101651024969</v>
       </c>
       <c r="G42">
-        <v>-0.05670718734006136</v>
+        <v>-0.06721321785032675</v>
       </c>
       <c r="H42">
-        <v>-0.06629023406001949</v>
+        <v>-0.07429205943172751</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1612,16 +1612,16 @@
         <v>-0</v>
       </c>
       <c r="E43">
-        <v>-0.8140287642557474</v>
+        <v>-0.7958501033700927</v>
       </c>
       <c r="F43">
-        <v>-0.820945162618709</v>
+        <v>-0.8057288135282917</v>
       </c>
       <c r="G43">
-        <v>-0.8634894556624833</v>
+        <v>-0.8258691488080011</v>
       </c>
       <c r="H43">
-        <v>-0.8751211403596555</v>
+        <v>-0.8431439279938523</v>
       </c>
     </row>
     <row r="44" spans="1:8">
